--- a/Bike-Repair-Source-Workbooks/Members-Capital-Steps.xlsx
+++ b/Bike-Repair-Source-Workbooks/Members-Capital-Steps.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ra1/Courses-Local/Instructional_Redesign_v2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ra1/Courses-Local/Instructional_Redesign_v2/Bike-Repair-Source-Workbooks/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_1C650E432F7AD18CA6D8CD44B90F15394E8A3C5B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_66362E51CD72D76842953D25B4E335036F894471" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="32120" yWindow="3040" windowWidth="38500" windowHeight="27280" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,9 +36,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="74">
-  <si>
-    <t>Statement of Members' Capital</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="77">
+  <si>
+    <t>Statement of Member's Capital</t>
   </si>
   <si>
     <t>For the period June 1 – August 31, 2026</t>
@@ -63,6 +63,15 @@
   </si>
   <si>
     <t>Owner's draw</t>
+  </si>
+  <si>
+    <t>Total Member's Capital, June 1, 2026</t>
+  </si>
+  <si>
+    <t>Change in total Member's Capital, June 1 to August 31, 2026</t>
+  </si>
+  <si>
+    <t>Total Member's Capital, August 31, 2026</t>
   </si>
   <si>
     <t>Cash — covered from your personal funds (May)</t>
@@ -333,7 +342,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -352,11 +361,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -376,6 +396,8 @@
     <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="41" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -704,7 +726,7 @@
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B5" s="4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D5" s="5">
         <v>160</v>
@@ -712,7 +734,7 @@
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B6" s="4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D6" s="5">
         <v>610</v>
@@ -720,7 +742,7 @@
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B7" s="4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D7" s="5">
         <v>220</v>
@@ -728,7 +750,7 @@
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B8" s="4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D8" s="5">
         <v>1300</v>
@@ -761,7 +783,7 @@
     </row>
     <row r="13" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B13" s="4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D13" s="5">
         <v>340</v>
@@ -769,7 +791,7 @@
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B14" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D14" s="5">
         <v>180</v>
@@ -777,7 +799,7 @@
     </row>
     <row r="15" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B15" s="4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D15" s="5">
         <v>80</v>
@@ -785,7 +807,7 @@
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B16" s="4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D16" s="5">
         <v>140</v>
@@ -793,7 +815,7 @@
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B17" s="4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D17" s="5">
         <v>130</v>
@@ -801,7 +823,7 @@
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B18" s="4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D18" s="5">
         <v>100</v>
@@ -809,7 +831,7 @@
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B19" s="4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D19" s="5">
         <v>150</v>
@@ -817,7 +839,7 @@
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B20" s="4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D20" s="5">
         <v>-300</v>
@@ -825,7 +847,7 @@
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B21" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D21" s="5">
         <v>-650</v>
@@ -843,7 +865,7 @@
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B23" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D23" s="5">
         <v>-650</v>
@@ -851,7 +873,7 @@
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B24" s="4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D24" s="5">
         <v>120</v>
@@ -859,7 +881,7 @@
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B25" s="4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D25" s="5">
         <v>-10</v>
@@ -867,7 +889,7 @@
     </row>
     <row r="26" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B26" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D26" s="5">
         <v>150</v>
@@ -875,7 +897,7 @@
     </row>
     <row r="27" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B27" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D27" s="5">
         <v>270</v>
@@ -883,7 +905,7 @@
     </row>
     <row r="28" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B28" s="4" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D28" s="5">
         <v>-25</v>
@@ -891,7 +913,7 @@
     </row>
     <row r="29" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B29" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D29" s="5">
         <v>300</v>
@@ -899,7 +921,7 @@
     </row>
     <row r="30" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B30" s="4" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D30" s="5">
         <v>-95</v>
@@ -907,7 +929,7 @@
     </row>
     <row r="31" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B31" s="4" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D31" s="5">
         <v>150</v>
@@ -915,7 +937,7 @@
     </row>
     <row r="32" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B32" s="4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D32" s="5">
         <v>360</v>
@@ -923,7 +945,7 @@
     </row>
     <row r="33" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B33" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D33" s="5">
         <v>-60</v>
@@ -931,7 +953,7 @@
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B34" s="4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D34" s="5">
         <v>225</v>
@@ -939,7 +961,7 @@
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B35" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D35" s="5">
         <v>-40</v>
@@ -947,7 +969,7 @@
     </row>
     <row r="36" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B36" s="4" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D36" s="5">
         <v>210</v>
@@ -955,7 +977,7 @@
     </row>
     <row r="37" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B37" s="4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D37" s="5">
         <v>-65</v>
@@ -963,7 +985,7 @@
     </row>
     <row r="38" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B38" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D38" s="5">
         <v>-650</v>
@@ -971,7 +993,7 @@
     </row>
     <row r="39" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B39" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D39" s="5">
         <v>240</v>
@@ -979,7 +1001,7 @@
     </row>
     <row r="40" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B40" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D40" s="5">
         <v>-35</v>
@@ -987,7 +1009,7 @@
     </row>
     <row r="41" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B41" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D41" s="5">
         <v>240</v>
@@ -995,7 +1017,7 @@
     </row>
     <row r="42" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B42" s="4" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D42" s="5">
         <v>-25</v>
@@ -1003,7 +1025,7 @@
     </row>
     <row r="43" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B43" s="4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D43" s="5">
         <v>450</v>
@@ -1011,7 +1033,7 @@
     </row>
     <row r="44" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B44" s="4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D44" s="5">
         <v>-125</v>
@@ -1019,7 +1041,7 @@
     </row>
     <row r="45" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B45" s="4" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D45" s="5">
         <v>360</v>
@@ -1027,7 +1049,7 @@
     </row>
     <row r="46" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B46" s="4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D46" s="5">
         <v>-55</v>
@@ -1035,7 +1057,7 @@
     </row>
     <row r="47" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B47" s="4" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D47" s="5">
         <v>270</v>
@@ -1043,7 +1065,7 @@
     </row>
     <row r="48" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B48" s="4" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D48" s="5">
         <v>-45</v>
@@ -1051,7 +1073,7 @@
     </row>
     <row r="49" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B49" s="4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D49" s="5">
         <v>240</v>
@@ -1059,7 +1081,7 @@
     </row>
     <row r="50" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B50" s="4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D50" s="5">
         <v>-100</v>
@@ -1067,7 +1089,7 @@
     </row>
     <row r="51" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B51" s="4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D51" s="5">
         <v>300</v>
@@ -1075,7 +1097,7 @@
     </row>
     <row r="52" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B52" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D52" s="5">
         <v>-80</v>
@@ -1083,7 +1105,7 @@
     </row>
     <row r="53" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B53" s="4" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D53" s="5">
         <v>-650</v>
@@ -1091,7 +1113,7 @@
     </row>
     <row r="54" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B54" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D54" s="5">
         <v>240</v>
@@ -1099,7 +1121,7 @@
     </row>
     <row r="55" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B55" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D55" s="5">
         <v>-25</v>
@@ -1107,7 +1129,7 @@
     </row>
     <row r="56" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B56" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D56" s="5">
         <v>485</v>
@@ -1115,7 +1137,7 @@
     </row>
     <row r="57" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B57" s="4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D57" s="5">
         <v>-129</v>
@@ -1123,7 +1145,7 @@
     </row>
     <row r="58" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B58" s="4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D58" s="5">
         <v>390</v>
@@ -1131,7 +1153,7 @@
     </row>
     <row r="59" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B59" s="4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D59" s="5">
         <v>-70</v>
@@ -1139,7 +1161,7 @@
     </row>
     <row r="60" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B60" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D60" s="5">
         <v>500</v>
@@ -1147,7 +1169,7 @@
     </row>
     <row r="61" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B61" s="4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D61" s="5">
         <v>-105</v>
@@ -1155,7 +1177,7 @@
     </row>
     <row r="62" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B62" s="4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D62" s="5">
         <v>300</v>
@@ -1163,7 +1185,7 @@
     </row>
     <row r="63" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B63" s="4" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D63" s="5">
         <v>-75</v>
@@ -1171,7 +1193,7 @@
     </row>
     <row r="64" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B64" s="4" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D64" s="5">
         <v>220</v>
@@ -1179,7 +1201,7 @@
     </row>
     <row r="65" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B65" s="4" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D65" s="5">
         <v>-36</v>
@@ -1187,7 +1209,7 @@
     </row>
     <row r="66" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B66" s="4" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D66" s="5">
         <v>-160</v>
@@ -1195,7 +1217,7 @@
     </row>
     <row r="67" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B67" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D67" s="5">
         <v>-40</v>
@@ -1203,7 +1225,7 @@
     </row>
     <row r="68" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B68" s="4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D68" s="5">
         <v>-30</v>
@@ -1226,7 +1248,7 @@
     </row>
     <row r="72" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B72" s="4" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D72" s="5">
         <v>-600</v>
@@ -1283,7 +1305,7 @@
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B6" s="4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D6" s="10">
         <v>0</v>
@@ -1314,7 +1336,7 @@
     </row>
     <row r="11" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B11" s="4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D11" s="5">
         <v>2640</v>
@@ -1345,7 +1367,7 @@
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B16" s="4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D16" s="5">
         <v>-600</v>
@@ -1391,7 +1413,7 @@
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.2">
       <c r="F3" s="11" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.2">
@@ -1409,13 +1431,13 @@
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B6" s="4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D6" s="10">
         <v>0</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.2">
@@ -1443,13 +1465,13 @@
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B11" s="4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D11" s="5">
         <v>2640</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.2">
@@ -1477,13 +1499,13 @@
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B16" s="4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D16" s="5">
         <v>-600</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.2">
@@ -1503,7 +1525,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="B1:D16"/>
+  <dimension ref="B1:D20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -1619,6 +1641,30 @@
         <v>-600</v>
       </c>
     </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="15">
+        <v>2460</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" s="17">
+        <v>2040</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B20" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20" s="18">
+        <v>4500</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Bike-Repair-Source-Workbooks/Members-Capital-Steps.xlsx
+++ b/Bike-Repair-Source-Workbooks/Members-Capital-Steps.xlsx
@@ -86,7 +86,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -116,11 +116,12 @@
       </bottom>
       <diagonal/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -142,6 +143,8 @@
     <xf numFmtId="41" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -507,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H68"/>
+  <dimension ref="B1:D68"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -584,7 +587,7 @@
           <t>Fixtures — Company received at formation (June 1)</t>
         </is>
       </c>
-      <c r="C9" s="7" t="n"/>
+      <c r="C9" s="20" t="n"/>
       <c r="D9" s="5" t="n">
         <v>750</v>
       </c>
@@ -595,7 +598,7 @@
           <t>Laptop — Company received at formation (June 1)</t>
         </is>
       </c>
-      <c r="C10" s="7" t="n"/>
+      <c r="C10" s="20" t="n"/>
       <c r="D10" s="5" t="n">
         <v>610</v>
       </c>
@@ -715,7 +718,7 @@
           <t>Parts used — Priya S.</t>
         </is>
       </c>
-      <c r="C22" s="7" t="n"/>
+      <c r="C22" s="20" t="n"/>
       <c r="D22" s="5" t="n">
         <v>-25</v>
       </c>

--- a/Bike-Repair-Source-Workbooks/Members-Capital-Steps.xlsx
+++ b/Bike-Repair-Source-Workbooks/Members-Capital-Steps.xlsx
@@ -541,7 +541,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="1" outlineLevel="1">
       <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Cash — Company received at formation (June 1)</t>
@@ -551,7 +551,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="1" outlineLevel="1">
       <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Right of Use — Company received at formation (June 1)</t>
@@ -561,7 +561,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="1" outlineLevel="1">
       <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Parts — Company received at formation (June 1)</t>
@@ -571,7 +571,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="1" outlineLevel="1">
       <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Tools &amp; Repair Equipment — Company received at formation (June 1)</t>
@@ -581,7 +581,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="1" outlineLevel="1">
       <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Fixtures — Company received at formation (June 1)</t>
@@ -592,7 +592,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="1" outlineLevel="1">
       <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Laptop — Company received at formation (June 1)</t>
@@ -603,7 +603,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="1" outlineLevel="1">
       <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Credit Card — Company assumed the claim at formation (June 1)</t>
@@ -613,7 +613,7 @@
         <v>-2030</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="1" outlineLevel="1">
       <c r="B12" s="4" t="inlineStr">
         <is>
           <t>Customer Deposit — Company assumed the claim at formation (June 1)</t>
@@ -623,7 +623,7 @@
         <v>-220</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" collapsed="1">
       <c r="B13" s="6" t="inlineStr">
         <is>
           <t>Balance, June 1, 2026</t>
@@ -672,7 +672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="1" outlineLevel="1">
       <c r="B18" s="4" t="inlineStr">
         <is>
           <t>Repair collected — Dana R.</t>
@@ -682,7 +682,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="1" outlineLevel="1">
       <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Parts used — Dana R.</t>
@@ -692,7 +692,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="1" outlineLevel="1">
       <c r="B20" s="4" t="inlineStr">
         <is>
           <t>Repair collected — Marcus T.</t>
@@ -702,7 +702,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="1" outlineLevel="1">
       <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Repair collected — Priya S.</t>
@@ -712,7 +712,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="1" outlineLevel="1">
       <c r="B22" s="4" t="inlineStr">
         <is>
           <t>Parts used — Priya S.</t>
@@ -723,7 +723,7 @@
         <v>-25</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="1" outlineLevel="1">
       <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Repair collected — Liam O.</t>
@@ -733,7 +733,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="1" outlineLevel="1">
       <c r="B24" s="4" t="inlineStr">
         <is>
           <t>Parts used — Liam O.</t>
@@ -743,7 +743,7 @@
         <v>-95</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="1" outlineLevel="1">
       <c r="B25" s="4" t="inlineStr">
         <is>
           <t>Repair collected — Sofia M.</t>
@@ -753,7 +753,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="1" outlineLevel="1">
       <c r="B26" s="4" t="inlineStr">
         <is>
           <t>Repair collected — Jamal W.</t>
@@ -763,7 +763,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="1" outlineLevel="1">
       <c r="B27" s="4" t="inlineStr">
         <is>
           <t>Parts used — Jamal W.</t>
@@ -773,7 +773,7 @@
         <v>-60</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="1" outlineLevel="1">
       <c r="B28" s="4" t="inlineStr">
         <is>
           <t>Repair collected — Erin K.</t>
@@ -783,7 +783,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="1" outlineLevel="1">
       <c r="B29" s="4" t="inlineStr">
         <is>
           <t>Parts used — Erin K.</t>
@@ -793,7 +793,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="1" outlineLevel="1">
       <c r="B30" s="4" t="inlineStr">
         <is>
           <t>Repair collected — Noah B.</t>
@@ -803,7 +803,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="1" outlineLevel="1">
       <c r="B31" s="4" t="inlineStr">
         <is>
           <t>Parts used — Noah B.</t>
@@ -813,7 +813,7 @@
         <v>-65</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="1" outlineLevel="1">
       <c r="B32" s="4" t="inlineStr">
         <is>
           <t>Rent used — June</t>
@@ -823,7 +823,7 @@
         <v>-650</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="1" outlineLevel="1">
       <c r="B33" s="4" t="inlineStr">
         <is>
           <t>Rent used — July</t>
@@ -833,7 +833,7 @@
         <v>-650</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="1" outlineLevel="1">
       <c r="B34" s="4" t="inlineStr">
         <is>
           <t>Repair collected — Grace L.</t>
@@ -843,7 +843,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="1" outlineLevel="1">
       <c r="B35" s="4" t="inlineStr">
         <is>
           <t>Parts used — Grace L.</t>
@@ -853,7 +853,7 @@
         <v>-35</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="1" outlineLevel="1">
       <c r="B36" s="4" t="inlineStr">
         <is>
           <t>Repair collected — Theo H.</t>
@@ -863,7 +863,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="1" outlineLevel="1">
       <c r="B37" s="4" t="inlineStr">
         <is>
           <t>Parts used — Theo H.</t>
@@ -873,7 +873,7 @@
         <v>-25</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="1" outlineLevel="1">
       <c r="B38" s="4" t="inlineStr">
         <is>
           <t>Repair collected — Maya P.</t>
@@ -883,7 +883,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="1" outlineLevel="1">
       <c r="B39" s="4" t="inlineStr">
         <is>
           <t>Parts used — Maya P.</t>
@@ -893,7 +893,7 @@
         <v>-125</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="1" outlineLevel="1">
       <c r="B40" s="4" t="inlineStr">
         <is>
           <t>Repair collected — Owen C.</t>
@@ -903,7 +903,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="1" outlineLevel="1">
       <c r="B41" s="4" t="inlineStr">
         <is>
           <t>Parts used — Owen C.</t>
@@ -913,7 +913,7 @@
         <v>-55</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="1" outlineLevel="1">
       <c r="B42" s="4" t="inlineStr">
         <is>
           <t>Repair collected — Ava D.</t>
@@ -923,7 +923,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="1" outlineLevel="1">
       <c r="B43" s="4" t="inlineStr">
         <is>
           <t>Parts used — Ava D.</t>
@@ -933,7 +933,7 @@
         <v>-45</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="1" outlineLevel="1">
       <c r="B44" s="4" t="inlineStr">
         <is>
           <t>Repair collected — Leo F.</t>
@@ -943,7 +943,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="1" outlineLevel="1">
       <c r="B45" s="4" t="inlineStr">
         <is>
           <t>Parts used — Leo F.</t>
@@ -953,7 +953,7 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="1" outlineLevel="1">
       <c r="B46" s="4" t="inlineStr">
         <is>
           <t>Repair collected — Nina V.</t>
@@ -963,7 +963,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="1" outlineLevel="1">
       <c r="B47" s="4" t="inlineStr">
         <is>
           <t>Parts used — Nina V.</t>
@@ -973,7 +973,7 @@
         <v>-80</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="1" outlineLevel="1">
       <c r="B48" s="4" t="inlineStr">
         <is>
           <t>Rent used — August</t>
@@ -983,7 +983,7 @@
         <v>-650</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="1" outlineLevel="1">
       <c r="B49" s="4" t="inlineStr">
         <is>
           <t>Repair collected — Caleb G.</t>
@@ -993,7 +993,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" hidden="1" outlineLevel="1">
       <c r="B50" s="4" t="inlineStr">
         <is>
           <t>Parts used — Caleb G.</t>
@@ -1003,7 +1003,7 @@
         <v>-25</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="1" outlineLevel="1">
       <c r="B51" s="4" t="inlineStr">
         <is>
           <t>Repair collected — Ruth A.</t>
@@ -1013,7 +1013,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="1" outlineLevel="1">
       <c r="B52" s="4" t="inlineStr">
         <is>
           <t>Parts used — Ruth A.</t>
@@ -1023,7 +1023,7 @@
         <v>-129</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="1" outlineLevel="1">
       <c r="B53" s="4" t="inlineStr">
         <is>
           <t>Repair collected — Sam Q.</t>
@@ -1033,7 +1033,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="1" outlineLevel="1">
       <c r="B54" s="4" t="inlineStr">
         <is>
           <t>Parts used — Sam Q.</t>
@@ -1043,7 +1043,7 @@
         <v>-70</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" hidden="1" outlineLevel="1">
       <c r="B55" s="4" t="inlineStr">
         <is>
           <t>Repair collected — Westville Bike Share</t>
@@ -1053,7 +1053,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="1" outlineLevel="1">
       <c r="B56" s="4" t="inlineStr">
         <is>
           <t>Parts used — Westville Bike Share</t>
@@ -1063,7 +1063,7 @@
         <v>-105</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" hidden="1" outlineLevel="1">
       <c r="B57" s="4" t="inlineStr">
         <is>
           <t>Repair delivered — Ridgeline Trail Crew, billed net 15 (unpaid)</t>
@@ -1073,7 +1073,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" hidden="1" outlineLevel="1">
       <c r="B58" s="4" t="inlineStr">
         <is>
           <t>Parts used — Ridgeline Trail Crew</t>
@@ -1083,7 +1083,7 @@
         <v>-75</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" hidden="1" outlineLevel="1">
       <c r="B59" s="4" t="inlineStr">
         <is>
           <t>Frame delivered — J. Smith (deposit earned)</t>
@@ -1093,7 +1093,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="1" outlineLevel="1">
       <c r="B60" s="4" t="inlineStr">
         <is>
           <t>Parts used — J. Smith</t>
@@ -1103,7 +1103,7 @@
         <v>-36</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" hidden="1" outlineLevel="1">
       <c r="B61" s="4" t="inlineStr">
         <is>
           <t>Depreciation — tools &amp; repair equipment, Summer 2026</t>
@@ -1113,7 +1113,7 @@
         <v>-160</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" hidden="1" outlineLevel="1">
       <c r="B62" s="4" t="inlineStr">
         <is>
           <t>Depreciation — fixtures, Summer 2026</t>
@@ -1123,7 +1123,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="1" outlineLevel="1">
       <c r="B63" s="4" t="inlineStr">
         <is>
           <t>Depreciation — laptop, Summer 2026</t>
@@ -1133,7 +1133,7 @@
         <v>-30</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" collapsed="1">
       <c r="B64" s="6" t="inlineStr">
         <is>
           <t>Balance, August 31, 2026</t>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="D66" s="5" t="n"/>
     </row>
-    <row r="67">
+    <row r="67" hidden="1" outlineLevel="1">
       <c r="B67" s="4" t="inlineStr">
         <is>
           <t>Owner's draw — money taken out for personal use</t>
@@ -1168,7 +1168,7 @@
         <v>-600</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" collapsed="1">
       <c r="B68" s="6" t="inlineStr">
         <is>
           <t>Balance, August 31, 2026</t>

--- a/Bike-Repair-Source-Workbooks/Members-Capital-Steps.xlsx
+++ b/Bike-Repair-Source-Workbooks/Members-Capital-Steps.xlsx
@@ -510,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:D68"/>
+  <dimension ref="A1:D68"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
     <row r="5" hidden="1" outlineLevel="1">
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Cash — Company received at formation (June 1)</t>
+          <t>Cash — additional contribution (Section 10)</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
@@ -633,7 +633,6 @@
       <c r="D13" s="8">
         <f>SUM(D5:D12)</f>
         <v>2460</v>
-        <v/>
       </c>
     </row>
     <row r="14">
@@ -646,7 +645,6 @@
       <c r="D14" s="8">
         <f>D13</f>
         <v>2460</v>
-        <v/>
       </c>
     </row>
     <row r="15">
@@ -1143,7 +1141,6 @@
       <c r="D64" s="8">
         <f>D17+SUM(D18:D63)</f>
         <v>2640</v>
-        <v/>
       </c>
     </row>
     <row r="65">
@@ -1178,7 +1175,6 @@
       <c r="D68" s="8">
         <f>SUM(D67:D67)</f>
         <v>-600</v>
-        <v/>
       </c>
     </row>
   </sheetData>
@@ -1192,7 +1188,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:D17"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1215,6 +1211,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="3" t="inlineStr">
         <is>
@@ -1252,9 +1249,9 @@
       <c r="D7" s="8">
         <f>D5+D6</f>
         <v>2460</v>
-        <v/>
-      </c>
-    </row>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
       <c r="B9" s="3" t="inlineStr">
         <is>
@@ -1292,9 +1289,9 @@
       <c r="D12" s="8">
         <f>D10+D11</f>
         <v>2640</v>
-        <v/>
-      </c>
-    </row>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="B14" s="3" t="inlineStr">
         <is>
@@ -1332,7 +1329,6 @@
       <c r="D17" s="8">
         <f>D15+D16</f>
         <v>-600</v>
-        <v/>
       </c>
     </row>
   </sheetData>
@@ -1346,7 +1342,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:F17"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1420,9 +1416,9 @@
       <c r="D7" s="8">
         <f>D5+D6</f>
         <v>2460</v>
-        <v/>
-      </c>
-    </row>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
       <c r="B9" s="3" t="inlineStr">
         <is>
@@ -1465,9 +1461,9 @@
       <c r="D12" s="8">
         <f>D10+D11</f>
         <v>2640</v>
-        <v/>
-      </c>
-    </row>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="B14" s="3" t="inlineStr">
         <is>
@@ -1510,7 +1506,6 @@
       <c r="D17" s="8">
         <f>D15+D16</f>
         <v>-600</v>
-        <v/>
       </c>
     </row>
   </sheetData>
@@ -1524,7 +1519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:D20"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1547,6 +1542,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="3" t="inlineStr">
         <is>
@@ -1576,7 +1572,6 @@
       <c r="D6" s="14">
         <f>D5</f>
         <v>2460</v>
-        <v/>
       </c>
     </row>
     <row r="7">
@@ -1621,7 +1616,6 @@
       <c r="D11" s="14">
         <f>D9+D10</f>
         <v>2640</v>
-        <v/>
       </c>
     </row>
     <row r="12">
@@ -1666,9 +1660,9 @@
       <c r="D16" s="14">
         <f>D14+D15</f>
         <v>-600</v>
-        <v/>
-      </c>
-    </row>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18">
       <c r="B18" t="inlineStr">
         <is>
